--- a/jpcore-r4/feature/swg2-dental/ValueSet-jp-dental-simple-presentteeth-observation-vs.xlsx
+++ b/jpcore-r4/feature/swg2-dental/ValueSet-jp-dental-simple-presentteeth-observation-vs.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_DentalSipmlePresentTeethObservation_VS</t>
+    <t>JP_DentalSimplePresentTeethObservation_VS</t>
   </si>
   <si>
     <t>Title</t>
